--- a/test_samples/TRANS_DAYA_PRIMA/sample3_ref.xlsx
+++ b/test_samples/TRANS_DAYA_PRIMA/sample3_ref.xlsx
@@ -744,7 +744,11 @@
           <t>PT. GLOSTAR INDONESIA</t>
         </is>
       </c>
-      <c r="E3" s="5" t="n"/>
+      <c r="E3" s="5" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
       <c r="F3" s="5" t="n"/>
       <c r="G3" s="5" t="n">
         <v>327250</v>
@@ -814,80 +818,80 @@
       <c r="A4" s="8" t="n">
         <v>46048</v>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>0188-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D4" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>LCL Lokal Serang - GSI-2 40"</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F4" s="10" t="n">
         <v>7560000</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>00053/TDP/SJ-01/2026</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K4" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L4" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M4" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N4" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O4" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P4" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q4" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R4" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -897,70 +901,75 @@
       <c r="A5" s="8" t="n">
         <v>46048</v>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>0188-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D5" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="n">
         <v>831600</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
+      <c r="I5" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J5" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L5" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M5" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N5" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O5" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P5" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q5" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R5" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1074,7 +1083,11 @@
           <t>PT. GLOSTAR INDONESIA</t>
         </is>
       </c>
-      <c r="E7" s="5" t="n"/>
+      <c r="E7" s="5" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
       <c r="F7" s="5" t="n"/>
       <c r="G7" s="5" t="n">
         <v>425700</v>
@@ -1144,80 +1157,80 @@
       <c r="A8" s="8" t="n">
         <v>46042</v>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>0144-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>L300 Serang GSI-2</t>
         </is>
       </c>
-      <c r="F8" t="n">
+      <c r="F8" s="10" t="n">
         <v>1840000</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H8" s="10" t="inlineStr">
         <is>
           <t>00037/TDP/SJ-01/2026</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
+      <c r="I8" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J8" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L8" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M8" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N8" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O8" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P8" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q8" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R8" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1227,75 +1240,80 @@
       <c r="A9" s="8" t="n">
         <v>46042</v>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>0144-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="G9" t="n">
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
+      <c r="G9" s="10" t="n">
         <v>202400</v>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
+      <c r="H9" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I9" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J9" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K9" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L9" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M9" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N9" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O9" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P9" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q9" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R9" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1765,7 +1783,11 @@
           <t>PT. GLOSTAR INDONESIA</t>
         </is>
       </c>
-      <c r="E15" s="5" t="n"/>
+      <c r="E15" s="5" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
       <c r="F15" s="5" t="n"/>
       <c r="G15" s="5" t="n">
         <v>1148400</v>
@@ -1835,80 +1857,80 @@
       <c r="A16" s="8" t="n">
         <v>46041</v>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>0131-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
+      <c r="C16" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D16" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E16" s="10" t="inlineStr">
         <is>
           <t>GSI-2 LCL Trucking 40"</t>
         </is>
       </c>
-      <c r="F16" t="n">
+      <c r="F16" s="10" t="n">
         <v>4920000</v>
       </c>
-      <c r="H16" t="inlineStr">
+      <c r="H16" s="10" t="inlineStr">
         <is>
           <t>GTO20260119-062</t>
         </is>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
+      <c r="I16" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J16" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K16" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L16" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M16" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N16" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O16" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P16" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q16" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R16" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -1918,80 +1940,80 @@
       <c r="A17" s="8" t="n">
         <v>46041</v>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B17" s="10" t="inlineStr">
         <is>
           <t>0131-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
+      <c r="C17" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D17" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E17" s="10" t="inlineStr">
         <is>
           <t>WING BOX GSI-2</t>
         </is>
       </c>
-      <c r="F17" t="n">
+      <c r="F17" s="10" t="n">
         <v>4284000</v>
       </c>
-      <c r="H17" t="inlineStr">
+      <c r="H17" s="10" t="inlineStr">
         <is>
           <t>GTO20260119-061</t>
         </is>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
+      <c r="I17" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J17" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K17" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L17" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M17" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N17" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O17" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P17" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q17" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R17" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2001,70 +2023,75 @@
       <c r="A18" s="8" t="n">
         <v>46041</v>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>0131-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="G18" t="n">
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D18" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
+      <c r="G18" s="10" t="n">
         <v>1012440</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
+      <c r="I18" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J18" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K18" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L18" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M18" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N18" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O18" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P18" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q18" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R18" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2177,7 +2204,11 @@
           <t>PT. GLOSTAR INDONESIA</t>
         </is>
       </c>
-      <c r="E20" s="5" t="n"/>
+      <c r="E20" s="5" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
       <c r="F20" s="5" t="n"/>
       <c r="G20" s="4" t="n">
         <v>281435</v>
@@ -2247,80 +2278,80 @@
       <c r="A21" s="8" t="n">
         <v>46036</v>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B21" s="10" t="inlineStr">
         <is>
           <t>0097-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
+      <c r="C21" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D21" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E21" s="10" t="inlineStr">
         <is>
           <t>GSI-2 LCL Trucking 40"</t>
         </is>
       </c>
-      <c r="F21" t="n">
+      <c r="F21" s="10" t="n">
         <v>4920000</v>
       </c>
-      <c r="H21" t="inlineStr">
+      <c r="H21" s="10" t="inlineStr">
         <is>
           <t>GTO20260113-065</t>
         </is>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
+      <c r="I21" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J21" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K21" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L21" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M21" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N21" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O21" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P21" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q21" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R21" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2330,80 +2361,80 @@
       <c r="A22" s="8" t="n">
         <v>46036</v>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B22" s="10" t="inlineStr">
         <is>
           <t>0097-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
+      <c r="C22" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D22" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E22" s="10" t="inlineStr">
         <is>
           <t>GSI-2 LCL Trucking 40"</t>
         </is>
       </c>
-      <c r="F22" t="n">
+      <c r="F22" s="10" t="n">
         <v>4920000</v>
       </c>
-      <c r="H22" t="inlineStr">
+      <c r="H22" s="10" t="inlineStr">
         <is>
           <t>GTO20260114-077</t>
         </is>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
+      <c r="I22" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J22" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K22" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L22" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M22" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N22" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O22" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P22" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q22" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R22" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2413,75 +2444,80 @@
       <c r="A23" s="8" t="n">
         <v>46036</v>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B23" s="10" t="inlineStr">
         <is>
           <t>0097-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="G23" t="n">
+      <c r="C23" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D23" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="n">
         <v>1082400</v>
       </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
+      <c r="H23" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I23" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J23" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K23" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L23" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M23" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N23" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O23" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P23" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q23" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R23" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2594,7 +2630,11 @@
           <t>PT. GLOSTAR INDONESIA</t>
         </is>
       </c>
-      <c r="E25" s="5" t="n"/>
+      <c r="E25" s="5" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
       <c r="F25" s="5" t="n"/>
       <c r="G25" s="4" t="n">
         <v>287980</v>
@@ -2664,80 +2704,80 @@
       <c r="A26" s="8" t="n">
         <v>46036</v>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>0110-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D26" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E26" s="10" t="inlineStr">
         <is>
           <t>Lokal CDD Tangerang-GSI-2</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F26" s="10" t="n">
         <v>2558500</v>
       </c>
-      <c r="H26" t="inlineStr">
+      <c r="H26" s="10" t="inlineStr">
         <is>
           <t>00029/TDP/SJ-01/2026</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R26" t="inlineStr">
+      <c r="I26" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J26" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K26" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L26" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M26" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N26" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O26" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P26" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q26" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R26" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2747,80 +2787,80 @@
       <c r="A27" s="8" t="n">
         <v>46036</v>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B27" s="10" t="inlineStr">
         <is>
           <t>0110-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
+      <c r="C27" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D27" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E27" s="10" t="inlineStr">
         <is>
           <t>Reimbursement of Inbound Expenses</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F27" s="10" t="n">
         <v>2247750</v>
       </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R27" t="inlineStr">
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I27" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J27" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K27" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L27" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M27" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N27" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O27" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P27" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q27" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R27" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -2830,75 +2870,80 @@
       <c r="A28" s="8" t="n">
         <v>46036</v>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>0110-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="G28" t="n">
+      <c r="C28" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D28" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
+      <c r="G28" s="10" t="n">
         <v>281435</v>
       </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R28" t="inlineStr">
+      <c r="H28" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I28" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J28" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K28" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L28" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M28" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N28" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O28" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P28" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q28" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R28" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3012,7 +3057,11 @@
           <t>PT. GLOSTAR INDONESIA</t>
         </is>
       </c>
-      <c r="E30" s="5" t="n"/>
+      <c r="E30" s="5" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
       <c r="F30" s="5" t="n"/>
       <c r="G30" s="5" t="n">
         <v>202400</v>
@@ -3082,80 +3131,80 @@
       <c r="A31" s="8" t="n">
         <v>46036</v>
       </c>
-      <c r="B31" t="inlineStr">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>0109-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D31" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E31" s="10" t="inlineStr">
         <is>
           <t>GSI-2 FCL Trucking 40"</t>
         </is>
       </c>
-      <c r="F31" t="n">
+      <c r="F31" s="10" t="n">
         <v>4920000</v>
       </c>
-      <c r="H31" t="inlineStr">
+      <c r="H31" s="10" t="inlineStr">
         <is>
           <t>GTO20260114-072</t>
         </is>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr">
+      <c r="I31" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J31" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K31" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L31" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M31" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N31" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O31" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P31" t="inlineStr">
+      <c r="O31" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P31" s="10" t="inlineStr">
         <is>
           <t>AS PENELOPE 604N</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
+      <c r="Q31" s="10" t="inlineStr">
         <is>
           <t>FANU3406216</t>
         </is>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="R31" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3165,80 +3214,80 @@
       <c r="A32" s="8" t="n">
         <v>46036</v>
       </c>
-      <c r="B32" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>0109-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>Handling GSI-2</t>
         </is>
       </c>
-      <c r="F32" t="n">
+      <c r="F32" s="10" t="n">
         <v>300000</v>
       </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr">
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I32" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J32" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L32" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M32" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N32" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O32" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P32" t="inlineStr">
+      <c r="O32" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P32" s="10" t="inlineStr">
         <is>
           <t>AS PENELOPE 604N</t>
         </is>
       </c>
-      <c r="Q32" t="inlineStr">
+      <c r="Q32" s="10" t="inlineStr">
         <is>
           <t>FANU3406216</t>
         </is>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="R32" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3248,80 +3297,80 @@
       <c r="A33" s="8" t="n">
         <v>46036</v>
       </c>
-      <c r="B33" t="inlineStr">
+      <c r="B33" s="10" t="inlineStr">
         <is>
           <t>0109-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D33" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E33" s="10" t="inlineStr">
         <is>
           <t>Biaya LOLO</t>
         </is>
       </c>
-      <c r="F33" t="n">
+      <c r="F33" s="10" t="n">
         <v>937950</v>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr">
+      <c r="H33" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I33" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J33" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K33" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L33" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M33" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N33" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O33" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P33" t="inlineStr">
+      <c r="O33" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P33" s="10" t="inlineStr">
         <is>
           <t>AS PENELOPE 604N</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
+      <c r="Q33" s="10" t="inlineStr">
         <is>
           <t>FANU3406216</t>
         </is>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="R33" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3331,80 +3380,80 @@
       <c r="A34" s="8" t="n">
         <v>46036</v>
       </c>
-      <c r="B34" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>0109-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
+      <c r="C34" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D34" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E34" s="10" t="inlineStr">
         <is>
           <t>Biaya Penumpukan</t>
         </is>
       </c>
-      <c r="F34" t="n">
+      <c r="F34" s="10" t="n">
         <v>819458</v>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr">
+      <c r="H34" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I34" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J34" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K34" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L34" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M34" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N34" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O34" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P34" t="inlineStr">
+      <c r="O34" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P34" s="10" t="inlineStr">
         <is>
           <t>AS PENELOPE 604N</t>
         </is>
       </c>
-      <c r="Q34" t="inlineStr">
+      <c r="Q34" s="10" t="inlineStr">
         <is>
           <t>FANU3406216</t>
         </is>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="R34" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3414,75 +3463,80 @@
       <c r="A35" s="8" t="n">
         <v>46036</v>
       </c>
-      <c r="B35" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>0109-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="G35" t="n">
+      <c r="C35" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D35" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="n">
         <v>574200</v>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr">
+      <c r="H35" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I35" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J35" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K35" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L35" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M35" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N35" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O35" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P35" t="inlineStr">
+      <c r="O35" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P35" s="10" t="inlineStr">
         <is>
           <t>AS PENELOPE 604N</t>
         </is>
       </c>
-      <c r="Q35" t="inlineStr">
+      <c r="Q35" s="10" t="inlineStr">
         <is>
           <t>FANU3406216</t>
         </is>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="R35" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3596,7 +3650,11 @@
           <t>PT. GLOSTAR INDONESIA</t>
         </is>
       </c>
-      <c r="E37" s="5" t="n"/>
+      <c r="E37" s="5" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
       <c r="F37" s="5" t="n"/>
       <c r="G37" s="5" t="n">
         <v>425700</v>
@@ -3666,80 +3724,80 @@
       <c r="A38" s="8" t="n">
         <v>46034</v>
       </c>
-      <c r="B38" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>0084-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D38" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>Lokal LCL 40" GSI-1 - GSI-2</t>
         </is>
       </c>
-      <c r="F38" t="n">
+      <c r="F38" s="10" t="n">
         <v>2880000</v>
       </c>
-      <c r="H38" t="inlineStr">
+      <c r="H38" s="10" t="inlineStr">
         <is>
           <t>00023/TDP/SJ-01/2026</t>
         </is>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R38" t="inlineStr">
+      <c r="I38" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J38" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K38" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L38" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N38" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O38" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P38" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q38" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R38" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3749,75 +3807,80 @@
       <c r="A39" s="8" t="n">
         <v>46034</v>
       </c>
-      <c r="B39" t="inlineStr">
+      <c r="B39" s="10" t="inlineStr">
         <is>
           <t>0084-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="G39" t="n">
+      <c r="C39" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="n">
         <v>316800</v>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R39" t="inlineStr">
+      <c r="H39" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I39" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J39" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M39" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N39" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O39" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P39" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q39" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R39" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3931,7 +3994,11 @@
           <t>PT. GLOSTAR INDONESIA</t>
         </is>
       </c>
-      <c r="E41" s="5" t="n"/>
+      <c r="E41" s="5" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
       <c r="F41" s="5" t="n"/>
       <c r="G41" s="5" t="n">
         <v>287980</v>
@@ -4001,80 +4068,80 @@
       <c r="A42" s="8" t="n">
         <v>46034</v>
       </c>
-      <c r="B42" t="inlineStr">
+      <c r="B42" s="10" t="inlineStr">
         <is>
           <t>0088-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
         <is>
           <t>GSI-2 FCL Trucking 20"</t>
         </is>
       </c>
-      <c r="F42" t="n">
+      <c r="F42" s="10" t="n">
         <v>4320000</v>
       </c>
-      <c r="H42" t="inlineStr">
+      <c r="H42" s="10" t="inlineStr">
         <is>
           <t>GTO20260112-021</t>
         </is>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr">
+      <c r="I42" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J42" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N42" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P42" t="inlineStr">
+      <c r="O42" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P42" s="10" t="inlineStr">
         <is>
           <t>KMTC SURABAYA 2510N</t>
         </is>
       </c>
-      <c r="Q42" t="inlineStr">
+      <c r="Q42" s="10" t="inlineStr">
         <is>
           <t>FTAU1069697</t>
         </is>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="R42" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4084,80 +4151,80 @@
       <c r="A43" s="8" t="n">
         <v>46034</v>
       </c>
-      <c r="B43" t="inlineStr">
+      <c r="B43" s="10" t="inlineStr">
         <is>
           <t>0088-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
+      <c r="C43" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
         <is>
           <t>Handling GSI-2</t>
         </is>
       </c>
-      <c r="F43" t="n">
+      <c r="F43" s="10" t="n">
         <v>300000</v>
       </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
+      <c r="H43" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I43" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J43" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K43" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L43" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N43" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P43" t="inlineStr">
+      <c r="O43" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P43" s="10" t="inlineStr">
         <is>
           <t>KMTC SURABAYA 2510N</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
+      <c r="Q43" s="10" t="inlineStr">
         <is>
           <t>FTAU1069697</t>
         </is>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="R43" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4167,80 +4234,80 @@
       <c r="A44" s="8" t="n">
         <v>46034</v>
       </c>
-      <c r="B44" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>0088-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D44" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E44" s="10" t="inlineStr">
         <is>
           <t>Biaya LOLO</t>
         </is>
       </c>
-      <c r="F44" t="n">
+      <c r="F44" s="10" t="n">
         <v>499500</v>
       </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr">
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I44" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J44" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K44" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L44" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N44" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O44" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P44" t="inlineStr">
+      <c r="O44" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P44" s="10" t="inlineStr">
         <is>
           <t>KMTC SURABAYA 2510N</t>
         </is>
       </c>
-      <c r="Q44" t="inlineStr">
+      <c r="Q44" s="10" t="inlineStr">
         <is>
           <t>FTAU1069697</t>
         </is>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="R44" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4250,80 +4317,80 @@
       <c r="A45" s="8" t="n">
         <v>46034</v>
       </c>
-      <c r="B45" t="inlineStr">
+      <c r="B45" s="10" t="inlineStr">
         <is>
           <t>0088-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
+      <c r="C45" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D45" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E45" s="10" t="inlineStr">
         <is>
           <t>Biaya Penumpukan</t>
         </is>
       </c>
-      <c r="F45" t="n">
+      <c r="F45" s="10" t="n">
         <v>613830</v>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr">
+      <c r="H45" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I45" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J45" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K45" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L45" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M45" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N45" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O45" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P45" t="inlineStr">
+      <c r="O45" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P45" s="10" t="inlineStr">
         <is>
           <t>KMTC SURABAYA 2510N</t>
         </is>
       </c>
-      <c r="Q45" t="inlineStr">
+      <c r="Q45" s="10" t="inlineStr">
         <is>
           <t>FTAU1069697</t>
         </is>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="R45" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4333,75 +4400,80 @@
       <c r="A46" s="8" t="n">
         <v>46034</v>
       </c>
-      <c r="B46" t="inlineStr">
+      <c r="B46" s="10" t="inlineStr">
         <is>
           <t>0088-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="G46" t="n">
+      <c r="C46" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="n">
         <v>508200</v>
       </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I46" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J46" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M46" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N46" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O46" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P46" t="inlineStr">
+      <c r="O46" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P46" s="10" t="inlineStr">
         <is>
           <t>KMTC SURABAYA 2510N</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr">
+      <c r="Q46" s="10" t="inlineStr">
         <is>
           <t>FTAU1069697</t>
         </is>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="R46" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4515,7 +4587,11 @@
           <t>PT. GLOSTAR INDONESIA</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n"/>
+      <c r="E48" s="5" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
       <c r="F48" s="5" t="n"/>
       <c r="G48" s="5" t="n">
         <v>541200</v>
@@ -4585,65 +4661,65 @@
       <c r="A49" s="8" t="n">
         <v>46031</v>
       </c>
-      <c r="B49" t="inlineStr">
+      <c r="B49" s="10" t="inlineStr">
         <is>
           <t>0076-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D49" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E49" s="10" t="inlineStr">
         <is>
           <t>GSI-2 FCL Trucking 40"</t>
         </is>
       </c>
-      <c r="F49" t="n">
+      <c r="F49" s="10" t="n">
         <v>4920000</v>
       </c>
-      <c r="H49" t="inlineStr">
+      <c r="H49" s="10" t="inlineStr">
         <is>
           <t>GTO20260109-065</t>
         </is>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N49" t="inlineStr">
+      <c r="I49" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J49" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K49" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L49" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M49" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N49" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O49" t="inlineStr">
+      <c r="O49" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4653,12 +4729,12 @@
           <t>MSC REBECCA III HU601A</t>
         </is>
       </c>
-      <c r="Q49" t="inlineStr">
+      <c r="Q49" s="10" t="inlineStr">
         <is>
           <t>TIIU4769488</t>
         </is>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="R49" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4668,65 +4744,65 @@
       <c r="A50" s="8" t="n">
         <v>46031</v>
       </c>
-      <c r="B50" t="inlineStr">
+      <c r="B50" s="10" t="inlineStr">
         <is>
           <t>0076-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
+      <c r="C50" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D50" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E50" s="10" t="inlineStr">
         <is>
           <t>Handling GSI-2</t>
         </is>
       </c>
-      <c r="F50" t="n">
+      <c r="F50" s="10" t="n">
         <v>300000</v>
       </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
+      <c r="H50" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I50" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J50" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K50" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L50" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M50" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N50" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O50" t="inlineStr">
+      <c r="O50" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4736,12 +4812,12 @@
           <t>MSC REBECCA III HU601A</t>
         </is>
       </c>
-      <c r="Q50" t="inlineStr">
+      <c r="Q50" s="10" t="inlineStr">
         <is>
           <t>TIIU4769488</t>
         </is>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="R50" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4751,65 +4827,65 @@
       <c r="A51" s="8" t="n">
         <v>46031</v>
       </c>
-      <c r="B51" t="inlineStr">
+      <c r="B51" s="10" t="inlineStr">
         <is>
           <t>0076-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
+      <c r="C51" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D51" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E51" s="10" t="inlineStr">
         <is>
           <t>Biaya LOLO</t>
         </is>
       </c>
-      <c r="F51" t="n">
+      <c r="F51" s="10" t="n">
         <v>1054500</v>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr">
+      <c r="H51" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I51" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J51" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K51" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L51" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M51" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N51" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O51" t="inlineStr">
+      <c r="O51" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4819,12 +4895,12 @@
           <t>MSC REBECCA III HU601A</t>
         </is>
       </c>
-      <c r="Q51" t="inlineStr">
+      <c r="Q51" s="10" t="inlineStr">
         <is>
           <t>TIIU4769488</t>
         </is>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="R51" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4834,65 +4910,65 @@
       <c r="A52" s="8" t="n">
         <v>46031</v>
       </c>
-      <c r="B52" t="inlineStr">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>0076-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D52" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E52" s="10" t="inlineStr">
         <is>
           <t>Biaya Penumpukan</t>
         </is>
       </c>
-      <c r="F52" t="n">
+      <c r="F52" s="10" t="n">
         <v>819458</v>
       </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr">
+      <c r="H52" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I52" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J52" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K52" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L52" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M52" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N52" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="O52" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4902,12 +4978,12 @@
           <t>MSC REBECCA III HU601A</t>
         </is>
       </c>
-      <c r="Q52" t="inlineStr">
+      <c r="Q52" s="10" t="inlineStr">
         <is>
           <t>TIIU4769488</t>
         </is>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="R52" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4917,60 +4993,65 @@
       <c r="A53" s="8" t="n">
         <v>46031</v>
       </c>
-      <c r="B53" t="inlineStr">
+      <c r="B53" s="10" t="inlineStr">
         <is>
           <t>0076-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="G53" t="n">
+      <c r="C53" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D53" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
+      <c r="G53" s="10" t="n">
         <v>574200</v>
       </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr">
+      <c r="H53" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I53" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J53" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K53" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L53" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M53" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N53" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O53" t="inlineStr">
+      <c r="O53" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -4980,12 +5061,12 @@
           <t>MSC REBECCA III HU601A</t>
         </is>
       </c>
-      <c r="Q53" t="inlineStr">
+      <c r="Q53" s="10" t="inlineStr">
         <is>
           <t>TIIU4769488</t>
         </is>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="R53" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5099,7 +5180,11 @@
           <t>PT. GLOSTAR INDONESIA</t>
         </is>
       </c>
-      <c r="E55" s="5" t="n"/>
+      <c r="E55" s="5" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
       <c r="F55" s="5" t="n"/>
       <c r="G55" s="5" t="n">
         <v>261800</v>
@@ -5169,80 +5254,80 @@
       <c r="A56" s="8" t="n">
         <v>46030</v>
       </c>
-      <c r="B56" t="inlineStr">
+      <c r="B56" s="10" t="inlineStr">
         <is>
           <t>0056-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
+      <c r="C56" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D56" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E56" s="10" t="inlineStr">
         <is>
           <t>Lokal CDD Serang - GSI-2</t>
         </is>
       </c>
-      <c r="F56" t="n">
+      <c r="F56" s="10" t="n">
         <v>2618000</v>
       </c>
-      <c r="H56" t="inlineStr">
+      <c r="H56" s="10" t="inlineStr">
         <is>
           <t>00011/TDP/SJ-01/2026</t>
         </is>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q56" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R56" t="inlineStr">
+      <c r="I56" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J56" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K56" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L56" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M56" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N56" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O56" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P56" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q56" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R56" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5252,75 +5337,80 @@
       <c r="A57" s="8" t="n">
         <v>46030</v>
       </c>
-      <c r="B57" t="inlineStr">
+      <c r="B57" s="10" t="inlineStr">
         <is>
           <t>0056-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="G57" t="n">
+      <c r="C57" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D57" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
+      <c r="G57" s="10" t="n">
         <v>387980</v>
       </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q57" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R57" t="inlineStr">
+      <c r="H57" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I57" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J57" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K57" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L57" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M57" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N57" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O57" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P57" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q57" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R57" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5701,7 +5791,11 @@
           <t>PT. GLOSTAR INDONESIA</t>
         </is>
       </c>
-      <c r="E62" s="5" t="n"/>
+      <c r="E62" s="5" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
       <c r="F62" s="5" t="n"/>
       <c r="G62" s="5" t="n">
         <v>574200</v>
@@ -5771,80 +5865,80 @@
       <c r="A63" s="8" t="n">
         <v>46029</v>
       </c>
-      <c r="B63" t="inlineStr">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>0055-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr">
+      <c r="C63" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D63" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E63" s="10" t="inlineStr">
         <is>
           <t>L300 Serang GSI-2</t>
         </is>
       </c>
-      <c r="F63" t="n">
+      <c r="F63" s="10" t="n">
         <v>1840000</v>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H63" s="10" t="inlineStr">
         <is>
           <t>00010/TDP/SJ-01/2026</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q63" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R63" t="inlineStr">
+      <c r="I63" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J63" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K63" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L63" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M63" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N63" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O63" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P63" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q63" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R63" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -5854,75 +5948,80 @@
       <c r="A64" s="8" t="n">
         <v>46029</v>
       </c>
-      <c r="B64" t="inlineStr">
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>0055-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="G64" t="n">
+      <c r="C64" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D64" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
+      <c r="G64" s="10" t="n">
         <v>202400</v>
       </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q64" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R64" t="inlineStr">
+      <c r="H64" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I64" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J64" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K64" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L64" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M64" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N64" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O64" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P64" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q64" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R64" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6125,7 +6224,11 @@
           <t>PT. GLOSTAR INDONESIA</t>
         </is>
       </c>
-      <c r="E67" s="5" t="n"/>
+      <c r="E67" s="5" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
       <c r="F67" s="5" t="n"/>
       <c r="G67" s="5" t="n">
         <v>1012440</v>
@@ -6195,80 +6298,80 @@
       <c r="A68" s="8" t="n">
         <v>46028</v>
       </c>
-      <c r="B68" t="inlineStr">
+      <c r="B68" s="10" t="inlineStr">
         <is>
           <t>0037-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr">
+      <c r="C68" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D68" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E68" s="10" t="inlineStr">
         <is>
           <t>GSI-2 FCL Trucking 40"</t>
         </is>
       </c>
-      <c r="F68" t="n">
+      <c r="F68" s="10" t="n">
         <v>4920000</v>
       </c>
-      <c r="H68" t="inlineStr">
+      <c r="H68" s="10" t="inlineStr">
         <is>
           <t>GTO20260106-084</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr">
+      <c r="I68" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J68" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K68" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L68" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M68" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N68" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O68" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P68" t="inlineStr">
+      <c r="O68" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P68" s="10" t="inlineStr">
         <is>
           <t>NYK DAEDALUS 098N</t>
         </is>
       </c>
-      <c r="Q68" t="inlineStr">
+      <c r="Q68" s="10" t="inlineStr">
         <is>
           <t>TLLU029775, ONEU2152586</t>
         </is>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="R68" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6278,80 +6381,80 @@
       <c r="A69" s="8" t="n">
         <v>46028</v>
       </c>
-      <c r="B69" t="inlineStr">
+      <c r="B69" s="10" t="inlineStr">
         <is>
           <t>0037-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr">
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D69" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E69" s="10" t="inlineStr">
         <is>
           <t>GSI-2 FCL Trucking 20"</t>
         </is>
       </c>
-      <c r="F69" t="n">
+      <c r="F69" s="10" t="n">
         <v>4320000</v>
       </c>
-      <c r="H69" t="inlineStr">
+      <c r="H69" s="10" t="inlineStr">
         <is>
           <t>GTO20260106-085</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N69" t="inlineStr">
+      <c r="I69" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J69" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K69" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L69" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M69" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N69" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O69" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P69" t="inlineStr">
+      <c r="O69" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P69" s="10" t="inlineStr">
         <is>
           <t>NYK DAEDALUS 098N</t>
         </is>
       </c>
-      <c r="Q69" t="inlineStr">
+      <c r="Q69" s="10" t="inlineStr">
         <is>
           <t>TLLU029775, ONEU2152586</t>
         </is>
       </c>
-      <c r="R69" t="inlineStr">
+      <c r="R69" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6361,80 +6464,80 @@
       <c r="A70" s="8" t="n">
         <v>46028</v>
       </c>
-      <c r="B70" t="inlineStr">
+      <c r="B70" s="10" t="inlineStr">
         <is>
           <t>0037-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr">
+      <c r="C70" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D70" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E70" s="10" t="inlineStr">
         <is>
           <t>Handling GSI-2</t>
         </is>
       </c>
-      <c r="F70" t="n">
+      <c r="F70" s="10" t="n">
         <v>600000</v>
       </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
+      <c r="H70" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I70" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J70" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K70" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L70" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M70" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N70" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P70" t="inlineStr">
+      <c r="O70" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P70" s="10" t="inlineStr">
         <is>
           <t>NYK DAEDALUS 098N</t>
         </is>
       </c>
-      <c r="Q70" t="inlineStr">
+      <c r="Q70" s="10" t="inlineStr">
         <is>
           <t>TLLU029775, ONEU2152586</t>
         </is>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="R70" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6444,80 +6547,80 @@
       <c r="A71" s="8" t="n">
         <v>46028</v>
       </c>
-      <c r="B71" t="inlineStr">
+      <c r="B71" s="10" t="inlineStr">
         <is>
           <t>0037-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr">
+      <c r="C71" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D71" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E71" s="10" t="inlineStr">
         <is>
           <t>Biaya LOLO JKTG00484400</t>
         </is>
       </c>
-      <c r="F71" t="n">
+      <c r="F71" s="10" t="n">
         <v>754800</v>
       </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
+      <c r="H71" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I71" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J71" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K71" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L71" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M71" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N71" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O71" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P71" t="inlineStr">
+      <c r="O71" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P71" s="10" t="inlineStr">
         <is>
           <t>NYK DAEDALUS 098N</t>
         </is>
       </c>
-      <c r="Q71" t="inlineStr">
+      <c r="Q71" s="10" t="inlineStr">
         <is>
           <t>TLLU029775, ONEU2152586</t>
         </is>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="R71" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6527,80 +6630,80 @@
       <c r="A72" s="8" t="n">
         <v>46028</v>
       </c>
-      <c r="B72" t="inlineStr">
+      <c r="B72" s="10" t="inlineStr">
         <is>
           <t>0037-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr">
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D72" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E72" s="10" t="inlineStr">
         <is>
           <t>Biaya Penumpukan JKTG00484400</t>
         </is>
       </c>
-      <c r="F72" t="n">
+      <c r="F72" s="10" t="n">
         <v>1942223</v>
       </c>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N72" t="inlineStr">
+      <c r="H72" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I72" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J72" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K72" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L72" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M72" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N72" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O72" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P72" t="inlineStr">
+      <c r="O72" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P72" s="10" t="inlineStr">
         <is>
           <t>NYK DAEDALUS 098N</t>
         </is>
       </c>
-      <c r="Q72" t="inlineStr">
+      <c r="Q72" s="10" t="inlineStr">
         <is>
           <t>TLLU029775, ONEU2152586</t>
         </is>
       </c>
-      <c r="R72" t="inlineStr">
+      <c r="R72" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6610,80 +6713,80 @@
       <c r="A73" s="8" t="n">
         <v>46028</v>
       </c>
-      <c r="B73" t="inlineStr">
+      <c r="B73" s="10" t="inlineStr">
         <is>
           <t>0037-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr">
+      <c r="C73" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D73" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E73" s="10" t="inlineStr">
         <is>
           <t>Biaya LOLO JKTG00505500</t>
         </is>
       </c>
-      <c r="F73" t="n">
+      <c r="F73" s="10" t="n">
         <v>599400</v>
       </c>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N73" t="inlineStr">
+      <c r="H73" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I73" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J73" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K73" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L73" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M73" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N73" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O73" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P73" t="inlineStr">
+      <c r="O73" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P73" s="10" t="inlineStr">
         <is>
           <t>NYK DAEDALUS 098N</t>
         </is>
       </c>
-      <c r="Q73" t="inlineStr">
+      <c r="Q73" s="10" t="inlineStr">
         <is>
           <t>TLLU029775, ONEU2152586</t>
         </is>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="R73" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6693,80 +6796,80 @@
       <c r="A74" s="8" t="n">
         <v>46028</v>
       </c>
-      <c r="B74" t="inlineStr">
+      <c r="B74" s="10" t="inlineStr">
         <is>
           <t>0037-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr">
+      <c r="C74" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D74" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E74" s="10" t="inlineStr">
         <is>
           <t>Biaya Penumpukan JKTG00505500</t>
         </is>
       </c>
-      <c r="F74" t="n">
+      <c r="F74" s="10" t="n">
         <v>1325340</v>
       </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N74" t="inlineStr">
+      <c r="H74" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I74" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J74" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K74" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L74" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M74" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N74" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O74" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P74" t="inlineStr">
+      <c r="O74" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P74" s="10" t="inlineStr">
         <is>
           <t>NYK DAEDALUS 098N</t>
         </is>
       </c>
-      <c r="Q74" t="inlineStr">
+      <c r="Q74" s="10" t="inlineStr">
         <is>
           <t>TLLU029775, ONEU2152586</t>
         </is>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="R74" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -6776,75 +6879,80 @@
       <c r="A75" s="8" t="n">
         <v>46028</v>
       </c>
-      <c r="B75" t="inlineStr">
+      <c r="B75" s="10" t="inlineStr">
         <is>
           <t>0037-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="G75" t="n">
+      <c r="C75" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D75" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
+      <c r="G75" s="10" t="n">
         <v>1082400</v>
       </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N75" t="inlineStr">
+      <c r="H75" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I75" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J75" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K75" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L75" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M75" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N75" s="10" t="inlineStr">
         <is>
           <t>USA</t>
         </is>
       </c>
-      <c r="O75" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P75" t="inlineStr">
+      <c r="O75" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P75" s="10" t="inlineStr">
         <is>
           <t>NYK DAEDALUS 098N</t>
         </is>
       </c>
-      <c r="Q75" t="inlineStr">
+      <c r="Q75" s="10" t="inlineStr">
         <is>
           <t>TLLU029775, ONEU2152586</t>
         </is>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="R75" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7492,7 +7600,11 @@
           <t>PT. GLOSTAR INDONESIA</t>
         </is>
       </c>
-      <c r="E83" s="5" t="n"/>
+      <c r="E83" s="5" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
       <c r="F83" s="5" t="n"/>
       <c r="G83" s="5" t="n">
         <v>1148400</v>
@@ -7562,80 +7674,80 @@
       <c r="A84" s="8" t="n">
         <v>46027</v>
       </c>
-      <c r="B84" t="inlineStr">
+      <c r="B84" s="10" t="inlineStr">
         <is>
           <t>0018-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E84" t="inlineStr">
+      <c r="C84" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D84" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E84" s="10" t="inlineStr">
         <is>
           <t>GSI-2 LCL Trucking 40"</t>
         </is>
       </c>
-      <c r="F84" t="n">
+      <c r="F84" s="10" t="n">
         <v>4920000</v>
       </c>
-      <c r="H84" t="inlineStr">
+      <c r="H84" s="10" t="inlineStr">
         <is>
           <t>GTO20260102-092</t>
         </is>
       </c>
-      <c r="I84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q84" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R84" t="inlineStr">
+      <c r="I84" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J84" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K84" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L84" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M84" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N84" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O84" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P84" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q84" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R84" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7645,80 +7757,80 @@
       <c r="A85" s="8" t="n">
         <v>46027</v>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B85" s="10" t="inlineStr">
         <is>
           <t>0018-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E85" t="inlineStr">
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D85" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E85" s="10" t="inlineStr">
         <is>
           <t>GSI-2 LCL Trucking 40"</t>
         </is>
       </c>
-      <c r="F85" t="n">
+      <c r="F85" s="10" t="n">
         <v>4920000</v>
       </c>
-      <c r="H85" t="inlineStr">
+      <c r="H85" s="10" t="inlineStr">
         <is>
           <t>GTO20260102-094</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q85" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R85" t="inlineStr">
+      <c r="I85" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J85" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K85" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L85" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M85" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N85" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O85" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P85" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q85" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R85" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7728,80 +7840,80 @@
       <c r="A86" s="8" t="n">
         <v>46027</v>
       </c>
-      <c r="B86" t="inlineStr">
+      <c r="B86" s="10" t="inlineStr">
         <is>
           <t>0018-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
+      <c r="C86" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D86" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E86" s="10" t="inlineStr">
         <is>
           <t>WING BOX GSI-2</t>
         </is>
       </c>
-      <c r="F86" t="n">
+      <c r="F86" s="10" t="n">
         <v>4284000</v>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H86" s="10" t="inlineStr">
         <is>
           <t>GTO20260102-087</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q86" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R86" t="inlineStr">
+      <c r="I86" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J86" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K86" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L86" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M86" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N86" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O86" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P86" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q86" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R86" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7811,80 +7923,80 @@
       <c r="A87" s="8" t="n">
         <v>46027</v>
       </c>
-      <c r="B87" t="inlineStr">
+      <c r="B87" s="10" t="inlineStr">
         <is>
           <t>0018-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E87" t="inlineStr">
+      <c r="C87" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D87" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E87" s="10" t="inlineStr">
         <is>
           <t>WING BOX GSI-2</t>
         </is>
       </c>
-      <c r="F87" t="n">
+      <c r="F87" s="10" t="n">
         <v>4284000</v>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H87" s="10" t="inlineStr">
         <is>
           <t>GTO20260102-091</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K87" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L87" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M87" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N87" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O87" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P87" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q87" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R87" t="inlineStr">
+      <c r="I87" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J87" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K87" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L87" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M87" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N87" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O87" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P87" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q87" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R87" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7894,75 +8006,80 @@
       <c r="A88" s="8" t="n">
         <v>46027</v>
       </c>
-      <c r="B88" t="inlineStr">
+      <c r="B88" s="10" t="inlineStr">
         <is>
           <t>0018-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="G88" t="n">
+      <c r="C88" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D88" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="n">
         <v>2024880</v>
       </c>
-      <c r="H88" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J88" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K88" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L88" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M88" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N88" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O88" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P88" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q88" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R88" t="inlineStr">
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I88" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J88" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K88" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L88" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M88" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N88" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O88" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P88" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q88" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R88" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8075,7 +8192,11 @@
           <t>PT. GLOSTAR INDONESIA</t>
         </is>
       </c>
-      <c r="E90" s="5" t="n"/>
+      <c r="E90" s="5" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
       <c r="F90" s="5" t="n"/>
       <c r="G90" s="4" t="n">
         <v>202400</v>
@@ -8141,80 +8262,80 @@
       <c r="A91" s="8" t="n">
         <v>46024</v>
       </c>
-      <c r="B91" t="inlineStr">
+      <c r="B91" s="10" t="inlineStr">
         <is>
           <t>0004-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="E91" t="inlineStr">
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D91" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E91" s="10" t="inlineStr">
         <is>
           <t>LCL-FUSO GSI-2</t>
         </is>
       </c>
-      <c r="F91" t="n">
+      <c r="F91" s="10" t="n">
         <v>2975000</v>
       </c>
-      <c r="H91" t="inlineStr">
+      <c r="H91" s="10" t="inlineStr">
         <is>
           <t>00001/TDP/SJ-01/2026</t>
         </is>
       </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q91" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R91" t="inlineStr">
+      <c r="I91" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J91" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K91" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L91" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M91" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N91" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O91" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P91" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q91" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R91" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -8224,75 +8345,80 @@
       <c r="A92" s="8" t="n">
         <v>46024</v>
       </c>
-      <c r="B92" t="inlineStr">
+      <c r="B92" s="10" t="inlineStr">
         <is>
           <t>0004-TDP-GSI2-I-2026</t>
         </is>
       </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>PT. TRANS DAYA PRIMA</t>
-        </is>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>PT. GLOSTAR INDONESIA</t>
-        </is>
-      </c>
-      <c r="G92" t="n">
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>PT. TRANS DAYA PRIMA</t>
+        </is>
+      </c>
+      <c r="D92" s="10" t="inlineStr">
+        <is>
+          <t>PT. GLOSTAR INDONESIA</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>VAT (11%)</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="n">
         <v>327250</v>
       </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="K92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="L92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="M92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="N92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="O92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="P92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="Q92" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="R92" t="inlineStr">
+      <c r="H92" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="I92" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="J92" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="K92" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="L92" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="M92" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="N92" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="O92" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="P92" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="Q92" s="10" t="inlineStr">
+        <is>
+          <t>N/A</t>
+        </is>
+      </c>
+      <c r="R92" s="10" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
